--- a/docs/RAFIQ Info.xlsx
+++ b/docs/RAFIQ Info.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\00 RAFIQ\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6871AC-BD9F-431E-93B9-3D0B6686A8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAF2AF8-B983-44A0-B4DE-178337645D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="199">
   <si>
     <t>scripts/start_phase5_apps.ps1</t>
   </si>
@@ -37,19 +40,793 @@
   </si>
   <si>
     <t>run</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Output</t>
+  </si>
+  <si>
+    <t>Acceptance</t>
+  </si>
+  <si>
+    <t>CP21C-G01</t>
+  </si>
+  <si>
+    <t>Case Matrix</t>
+  </si>
+  <si>
+    <t>Machine-readable 20+ case matrix.</t>
+  </si>
+  <si>
+    <t>Covers required groups and excludes/escalates sensitive prompts correctly.</t>
+  </si>
+  <si>
+    <t>CP21C-G02</t>
+  </si>
+  <si>
+    <t>Evidence Collector</t>
+  </si>
+  <si>
+    <t>Current private API/search/orchestrator evidence captured per case.</t>
+  </si>
+  <si>
+    <t>Every case has response state and selected evidence or blocked reason.</t>
+  </si>
+  <si>
+    <t>CP21C-G03</t>
+  </si>
+  <si>
+    <t>Graph Export</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Private </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>resource-graph.json</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Manifest, nodes, edges, statuses, release states, access levels pass contract checks.</t>
+  </si>
+  <si>
+    <t>CP21C-G04</t>
+  </si>
+  <si>
+    <t>Vault Packs</t>
+  </si>
+  <si>
+    <t>Private ranking case markdown packs.</t>
+  </si>
+  <si>
+    <t>Every pack has required front matter and scoring sections.</t>
+  </si>
+  <si>
+    <t>CP21C-G05</t>
+  </si>
+  <si>
+    <t>Score Summary</t>
+  </si>
+  <si>
+    <t>Ranking summary and remediation list.</t>
+  </si>
+  <si>
+    <t>Average score &gt;= 85, no critical case &lt; 75, remediation exists for defects.</t>
+  </si>
+  <si>
+    <t>CP21C-G06</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <r>
+      <t>check_cp21c_resource_graphify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> script.</t>
+    </r>
+  </si>
+  <si>
+    <t>Script verifies matrix, graph, packs, scores, and no unsafe ordinary guidance.</t>
+  </si>
+  <si>
+    <t>CP21C-G07</t>
+  </si>
+  <si>
+    <t>Close-Out</t>
+  </si>
+  <si>
+    <t>CP21C docs/checklist/decision updates.</t>
+  </si>
+  <si>
+    <t>Completed, next planned, ad-hoc first, checklist update, documentation update recorded.</t>
+  </si>
+  <si>
+    <t>2. Baseline</t>
+  </si>
+  <si>
+    <t>CP25 starts after:</t>
+  </si>
+  <si>
+    <t>| Baseline | Status | Evidence |</t>
+  </si>
+  <si>
+    <t>| --- | --- | --- |</t>
+  </si>
+  <si>
+    <t>| CP22 full private resource graph and vault | Complete | `CP22_G10_CLOSE_OUT_REPORT.md` |</t>
+  </si>
+  <si>
+    <t>| CP23 reviewer workflow and internal UI contracts | Complete | `CP23_A04_REVIEWER_WORKFLOW_CONTRACT.md`; `CP23_A05_INTERNAL_UI_WORKBENCH_PLAN.md` |</t>
+  </si>
+  <si>
+    <t>| CP23 close-out | Complete | `CP23_A10_CLOSE_OUT_AND_NEXT_SCOPE_DECISION_REPORT.md` |</t>
+  </si>
+  <si>
+    <t>| CP24 graph-aware retrieval prototype | Complete | `CP24_G09_CLOSE_OUT_AND_NEXT_SCOPE_DECISION.md` |</t>
+  </si>
+  <si>
+    <t>| CP24 combined verifier | Passing | `scripts/check_cp24_close_out.mjs` |</t>
+  </si>
+  <si>
+    <t>Inherited facts:</t>
+  </si>
+  <si>
+    <t>## 6. Checkpoints</t>
+  </si>
+  <si>
+    <t>### CP25-A01 - Action Workflow Architecture And Case Matrix</t>
+  </si>
+  <si>
+    <t>Purpose: define the reviewer action workflow before implementation.</t>
+  </si>
+  <si>
+    <t>Status: Complete. See `CP25_A01_ACTION_WORKFLOW_ARCHITECTURE_AND_CASE_MATRIX.md`.</t>
+  </si>
+  <si>
+    <t>Deliverables:</t>
+  </si>
+  <si>
+    <t>- action workflow architecture note,</t>
+  </si>
+  <si>
+    <t>- action and role matrix,</t>
+  </si>
+  <si>
+    <t>- CP24 fixture-to-review-case map,</t>
+  </si>
+  <si>
+    <t>- allowed state transition table,</t>
+  </si>
+  <si>
+    <t>- required notes policy,</t>
+  </si>
+  <si>
+    <t>Acceptance:</t>
+  </si>
+  <si>
+    <t>- CP24 close-out is the controlling baseline;</t>
+  </si>
+  <si>
+    <t>- reviewer actions are private-only;</t>
+  </si>
+  <si>
+    <t>- public publication is explicitly out of scope;</t>
+  </si>
+  <si>
+    <t>- high/critical/escalation/public-boundary actions require notes;</t>
+  </si>
+  <si>
+    <t>### CP25-A02 - Request, Response, And State Contracts</t>
+  </si>
+  <si>
+    <t>Purpose: turn CP23-A04 and CP24 handoff outputs into concrete CP25 shared contracts.</t>
+  </si>
+  <si>
+    <t>Status: Complete. See `CP25_A02_REQUEST_RESPONSE_AND_STATE_CONTRACTS.md`.</t>
+  </si>
+  <si>
+    <t>- reviewer action request contract,</t>
+  </si>
+  <si>
+    <t>- reviewer action response contract,</t>
+  </si>
+  <si>
+    <t>- review queue item contract extension,</t>
+  </si>
+  <si>
+    <t>- remediation state contract,</t>
+  </si>
+  <si>
+    <t>- audit event contract,</t>
+  </si>
+  <si>
+    <t>- action target IDs are explicit;</t>
+  </si>
+  <si>
+    <t>- from/to status and actor role are required;</t>
+  </si>
+  <si>
+    <t>- required notes are enforceable;</t>
+  </si>
+  <si>
+    <t>- public-safe and publication fields remain false by default;</t>
+  </si>
+  <si>
+    <t>### CP25-A03 - Review Queue And Remediation State Export</t>
+  </si>
+  <si>
+    <t>Purpose: generate bounded private workbench state from CP24 outputs.</t>
+  </si>
+  <si>
+    <t>Status: Complete. See `CP25_A03_REVIEW_QUEUE_AND_REMEDIATION_STATE_EXPORT.md`.</t>
+  </si>
+  <si>
+    <t>- review queue export,</t>
+  </si>
+  <si>
+    <t>- remediation state export,</t>
+  </si>
+  <si>
+    <t>- role assignment summary,</t>
+  </si>
+  <si>
+    <t>- severity and blocker summary,</t>
+  </si>
+  <si>
+    <t>- unresolved reference report,</t>
+  </si>
+  <si>
+    <t>- all 72 CP24 remediation items are represented or explicitly deferred;</t>
+  </si>
+  <si>
+    <t>- high/critical blockers remain visible;</t>
+  </si>
+  <si>
+    <t>- queue items reference CP24 route/candidate/remediation IDs;</t>
+  </si>
+  <si>
+    <t>- graph/vault IDs resolve through CP22/CP24 indexes;</t>
+  </si>
+  <si>
+    <t>### CP25-A04 - Audit Event And Decision Ledger</t>
+  </si>
+  <si>
+    <t>Purpose: create a bounded audit trail model for reviewer actions.</t>
+  </si>
+  <si>
+    <t>Status: Complete. See `CP25_A04_AUDIT_EVENT_AND_DECISION_LEDGER.md`.</t>
+  </si>
+  <si>
+    <t>- audit event schema,</t>
+  </si>
+  <si>
+    <t>- decision ledger artifact,</t>
+  </si>
+  <si>
+    <t>- action-to-transition verifier,</t>
+  </si>
+  <si>
+    <t>- required notes verifier,</t>
+  </si>
+  <si>
+    <t>- previous/new status diff model,</t>
+  </si>
+  <si>
+    <t>- every action creates an audit event;</t>
+  </si>
+  <si>
+    <t>- each event records actor role, action, target, from status, to status, reason/notes, timestamp, and affected refs;</t>
+  </si>
+  <si>
+    <t>- invalid transitions fail verification;</t>
+  </si>
+  <si>
+    <t>- missing required notes fail verification;</t>
+  </si>
+  <si>
+    <t>### CP25-A05 - Private API Prototype</t>
+  </si>
+  <si>
+    <t>Purpose: expose CP25 action workflow behind private API only.</t>
+  </si>
+  <si>
+    <t>Status: Complete. See `CP25_A05_PRIVATE_API_PROTOTYPE.md`.</t>
+  </si>
+  <si>
+    <t>- private reviewer action route,</t>
+  </si>
+  <si>
+    <t>- private remediation transition route,</t>
+  </si>
+  <si>
+    <t>- private audit/ledger preview route,</t>
+  </si>
+  <si>
+    <t>- service methods,</t>
+  </si>
+  <si>
+    <t>- OpenAPI private DTOs,</t>
+  </si>
+  <si>
+    <t>- routes live under private content namespace;</t>
+  </si>
+  <si>
+    <t>- no public route is introduced;</t>
+  </si>
+  <si>
+    <t>- invalid actions fail safely;</t>
+  </si>
+  <si>
+    <t>- payloads are bounded and do not dump full graph/vault data;</t>
+  </si>
+  <si>
+    <t>### CP25-A06 - Internal UI Action Controls</t>
+  </si>
+  <si>
+    <t>Purpose: make CP25 actions usable in RAFIQ internal UI.</t>
+  </si>
+  <si>
+    <t>- action selector,</t>
+  </si>
+  <si>
+    <t>- required notes field,</t>
+  </si>
+  <si>
+    <t>- role/status display,</t>
+  </si>
+  <si>
+    <t>- audit preview,</t>
+  </si>
+  <si>
+    <t>- remediation state controls,</t>
+  </si>
+  <si>
+    <t>- public-boundary warning,</t>
+  </si>
+  <si>
+    <t>- private mode ribbon remains visible;</t>
+  </si>
+  <si>
+    <t>- action controls are private-only;</t>
+  </si>
+  <si>
+    <t>- required notes are visible before submit;</t>
+  </si>
+  <si>
+    <t>- risky actions have confirmation copy;</t>
+  </si>
+  <si>
+    <t>- public-release blocked state remains visible;</t>
+  </si>
+  <si>
+    <t>### CP25-A07 - Audit Export And Remediation Review Proof</t>
+  </si>
+  <si>
+    <t>Purpose: prove reviewer actions and remediation workflow outputs can be exported and inspected.</t>
+  </si>
+  <si>
+    <t>- audit event export,</t>
+  </si>
+  <si>
+    <t>- remediation transition export,</t>
+  </si>
+  <si>
+    <t>- reviewer workload summary,</t>
+  </si>
+  <si>
+    <t>- blocker summary,</t>
+  </si>
+  <si>
+    <t>- unresolved action report,</t>
+  </si>
+  <si>
+    <t>- audit exports are private-only;</t>
+  </si>
+  <si>
+    <t>- remediation transitions link back to original CP24 items;</t>
+  </si>
+  <si>
+    <t>- open blockers remain visible;</t>
+  </si>
+  <si>
+    <t>- resolved/deferred/rejected states preserve history;</t>
+  </si>
+  <si>
+    <t>### CP25-A08 - Combined Verification</t>
+  </si>
+  <si>
+    <t>Purpose: provide one command that verifies CP22, CP23, CP24, and CP25 workflow boundaries.</t>
+  </si>
+  <si>
+    <t>- combined verifier,</t>
+  </si>
+  <si>
+    <t>- inherited CP24 close-out verifier,</t>
+  </si>
+  <si>
+    <t>- CP25 contract checks,</t>
+  </si>
+  <si>
+    <t>- transition/audit checks,</t>
+  </si>
+  <si>
+    <t>- private API/UI checks,</t>
+  </si>
+  <si>
+    <t>- CP24 close-out still passes;</t>
+  </si>
+  <si>
+    <t>- all CP25 generated action/audit/remediation artifacts pass schema checks;</t>
+  </si>
+  <si>
+    <t>- invalid transitions and missing required notes are rejected;</t>
+  </si>
+  <si>
+    <t>- no public CP25 route exists;</t>
+  </si>
+  <si>
+    <t>- public-safe counts remain zero;</t>
+  </si>
+  <si>
+    <t>- no secrets or `.env` values are printed.</t>
+  </si>
+  <si>
+    <t>### CP25-A09 - Close-Out And Next Scope Decision</t>
+  </si>
+  <si>
+    <t>Purpose: close CP25 and decide whether to proceed to CP26 live snapshot export, CP27 public release gate simulation, or CP28 approved public study pack track.</t>
+  </si>
+  <si>
+    <t>- close-out report,</t>
+  </si>
+  <si>
+    <t>- final checklist,</t>
+  </si>
+  <si>
+    <t>- known limitations,</t>
+  </si>
+  <si>
+    <t>- CP25 combined verifier passes;</t>
+  </si>
+  <si>
+    <t>- action workflow limits are documented;</t>
+  </si>
+  <si>
+    <t>- public release remains blocked unless a separate public-release track explicitly approves otherwise;</t>
+  </si>
+  <si>
+    <t>## 7. Acceptance Gates</t>
+  </si>
+  <si>
+    <t>CP25 cannot close unless:</t>
+  </si>
+  <si>
+    <t>- `node scripts\check_cp24_close_out.mjs` remains passing;</t>
+  </si>
+  <si>
+    <t>- CP25 combined verifier exists and passes;</t>
+  </si>
+  <si>
+    <t>- reviewer actions produce audit events;</t>
+  </si>
+  <si>
+    <t>- invalid transitions are rejected;</t>
+  </si>
+  <si>
+    <t>- required notes are enforced;</t>
+  </si>
+  <si>
+    <t>- remediation state changes preserve history;</t>
+  </si>
+  <si>
+    <t>- high/critical/escalation/public-boundary blockers remain visible;</t>
+  </si>
+  <si>
+    <t>- no public route exposes CP25 private workflow data;</t>
+  </si>
+  <si>
+    <t>- rollback and verifier plan.</t>
+  </si>
+  <si>
+    <t>- CP23 role/action/status contract is preserved or explicitly extended.</t>
+  </si>
+  <si>
+    <t>- public-boundary contract.</t>
+  </si>
+  <si>
+    <t>- graph/vault refs remain separate from canonical refs.</t>
+  </si>
+  <si>
+    <t>- manifest and checksums.</t>
+  </si>
+  <si>
+    <t>- public-safe counts remain zero.</t>
+  </si>
+  <si>
+    <t>- immutable event ordering rules.</t>
+  </si>
+  <si>
+    <t>- no event publishes content.</t>
+  </si>
+  <si>
+    <t>- verifier.</t>
+  </si>
+  <si>
+    <t>- reviewer actions cannot mark public-safe artifacts.</t>
+  </si>
+  <si>
+    <t>- mobile/desktop layout proof.</t>
+  </si>
+  <si>
+    <t>- no public route exposes CP25 workflow data.</t>
+  </si>
+  <si>
+    <t>- checksum manifest.</t>
+  </si>
+  <si>
+    <t>- public boundary checks.</t>
+  </si>
+  <si>
+    <t>- next scope recommendation.</t>
+  </si>
+  <si>
+    <t>- next scope is selected with rationale.</t>
+  </si>
+  <si>
+    <t>- docs and verifier commands are updated.</t>
+  </si>
+  <si>
+    <r>
+      <t>CP26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> snapshot export and refresh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> refresh-backed graph and vault rebuild</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> retrieval engine from refreshed graph</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reviewer workbench productionization</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> private MVP guidance loop integration</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> internal product UX completion</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> data quality and remediation burn-down</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP33</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> private production architecture hardening</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP34</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> internal QA/UAT/regression</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> private stakeholder demo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> private product completion hardening</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CP37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> public release gate simulation only</t>
+    </r>
+  </si>
+  <si>
+    <t>CP26 is the current active sprint.</t>
+  </si>
+  <si>
+    <t>CP27-CP29 are the private Graphify/data/reviewer foundation.</t>
+  </si>
+  <si>
+    <t>CP30-CP31 are the actual private product experience integration.</t>
+  </si>
+  <si>
+    <t>CP32-CP34 are quality, operations, QA, and UAT.</t>
+  </si>
+  <si>
+    <t>CP35-CP36 are private demo and final hardening.</t>
+  </si>
+  <si>
+    <t>CP37 is only a public-release simulation, still blocked.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -72,8 +849,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,13 +1143,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -369,12 +1157,1060 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB2383C-9704-45D6-866E-FFE3549897CE}">
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="82.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79930673-0684-4FA3-8868-754B3067F5A4}">
+  <dimension ref="B3:B232"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="155.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2">
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2">
+      <c r="B214" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2">
+      <c r="B219" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2">
+      <c r="B221" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2">
+      <c r="B232" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479B6F19-801D-4FF6-A313-AABE470ACBD1}">
+  <dimension ref="B3:D14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="59.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4">
+      <c r="B3" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="B12" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
